--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andres/Documents/GitHub/AMOC_Figures_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D8DE41-B4D0-3345-BA5F-E5ABD73340E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40552C1-51FD-F348-AE59-72B8DF2874ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="660" windowWidth="24960" windowHeight="11800" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="20800" windowHeight="16940" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="53">
   <si>
     <t>Chapter</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>To add sources, leave them in the feedback. Andrés will then place them here.</t>
+  </si>
+  <si>
+    <t>Risk has many dimensions that depend on regional contexts.</t>
+  </si>
+  <si>
+    <t>Risks will differ with a larger AMOC weakening compared to a smaller weakening.</t>
   </si>
 </sst>
 </file>
@@ -543,7 +549,7 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="57.33203125" customWidth="1"/>
+    <col min="4" max="4" width="96.83203125" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -659,7 +665,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -685,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>

--- a/Figures.xlsx
+++ b/Figures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andres/Documents/GitHub/AMOC_Figures_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40552C1-51FD-F348-AE59-72B8DF2874ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3610D1E8-EB76-954B-8965-D0CF7DA9DCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="20800" windowHeight="16940" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
+    <workbookView xWindow="920" yWindow="4080" windowWidth="29200" windowHeight="14120" xr2:uid="{D6B1EF31-B44C-C14C-87F3-F58189DEBE44}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="55">
   <si>
     <t>Chapter</t>
   </si>
@@ -195,16 +195,29 @@
   </si>
   <si>
     <t>Risks will differ with a larger AMOC weakening compared to a smaller weakening.</t>
+  </si>
+  <si>
+    <t>Gaurav Madan</t>
+  </si>
+  <si>
+    <t>Jon Robson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -230,8 +243,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,6 +946,9 @@
       <c r="D16" t="s">
         <v>25</v>
       </c>
+      <c r="F16" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="G16" t="s">
         <v>50</v>
       </c>
@@ -955,6 +972,9 @@
       <c r="D17" t="s">
         <v>27</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="G17" t="s">
         <v>50</v>
       </c>
@@ -1069,6 +1089,9 @@
       </c>
       <c r="D22" t="s">
         <v>31</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="G22" t="s">
         <v>50</v>
